--- a/04_DESIGN_TABLES/DesignTable_2606.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2606.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,55 +461,60 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>PORTDEPTH@BORE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>THDMAJ_B1@DRIVE</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>THDMAJ_A@DRIVE</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>THDMAJ_B3@DRIVE</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>$PRP@TubeOD</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>$PRP@PartNo</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>$PRP@Threads</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>$PRP@DataStatus</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>$PRP@AxialSource</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>$COMMENT</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>$PRP@ScopeAction</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -542,46 +547,46 @@
       <c r="H3" t="n">
         <v>0.43</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.4375</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.54</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0.4375</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>1/4-1/4</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2606-04-04-04</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>7/16-20 (B (1) UN/UNF-2A) x 1/4-18 (A NPTF) x 7/16-20 (B (3) UN/UNF-2A)</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Air-Way s174 only (double-pass 7 rows)</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 2606-04-04-04-FG</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -614,46 +619,46 @@
       <c r="H4" t="n">
         <v>0.43</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.5625</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.54</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0.5625</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>3/8-3/8</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>2606-06-04-06</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>9/16-18 (B (1) UN/UNF-2A) x 1/4-18 (A NPTF) x 9/16-18 (B (3) UN/UNF-2A)</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Air-Way s174 only (double-pass 7 rows)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -686,46 +691,46 @@
       <c r="H5" t="n">
         <v>0.57</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.5625</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.675</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0.5625</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>3/8-3/8</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>2606-06-06-06</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>9/16-18 (B (1) UN/UNF-2A) x 3/8-18 (A NPTF) x 9/16-18 (B (3) UN/UNF-2A)</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Air-Way s174 only (double-pass 7 rows)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 2606-06-06-06-FG</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -758,46 +763,46 @@
       <c r="H6" t="n">
         <v>0.57</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.75</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.675</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>0.75</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1/2-1/2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>2606-08-06-08</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>3/4-16 (B (1) UN/UNF-2A) x 3/8-18 (A NPTF) x 3/4-16 (B (3) UN/UNF-2A)</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Air-Way s174 only (double-pass 7 rows)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -830,46 +835,46 @@
       <c r="H7" t="n">
         <v>0.7</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.75</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0.84</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.75</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1/2-1/2</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>2606-08-08-08</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>3/4-16 (B (1) UN/UNF-2A) x 1/2-14 (A NPTF) x 3/4-16 (B (3) UN/UNF-2A)</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Air-Way s174 only (double-pass 7 rows)</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 2606-08-08-08-FG</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -902,46 +907,46 @@
       <c r="H8" t="n">
         <v>1.14</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>1.3125</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>1.315</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>1.3125</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>2606-16-16-16</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>1 5/16-12 (B (1) UN/UNF-2A) x 1-11 1/2 (A NPTF) x 1 5/16-12 (B (3) UN/UNF-2A)</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Air-Way s174 only (double-pass 7 rows)</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 2606-16-16-16-FG</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -974,46 +979,46 @@
       <c r="H9" t="n">
         <v>1.48</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1.625</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>1.66</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>1.625</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1 1/4-1 1/4</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2606-20-20-20</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>1 5/8-12 (B (1) UN/UNF-2A) x 1 1/4-11 1/2 (A NPTF) x 1 5/8-12 (B (3) UN/UNF-2A)</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Air-Way s174 only (double-pass 7 rows)</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1025,32 +1030,62 @@
           <t>2606-04-04-04-FG</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="B10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>2606-04-04-04-FG</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2606-04-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2606-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / L 1 / Hex Flat / Side 1 ID / Side 3 ID = JIC run leg / female pipe run leg / JIC branch leg / body hex / JIC bores (Brennan TFA catalog p51 drawing M / L / N / Y / B1 / B3; Brennan 2606-08-08-08-FG STEP: 1.520 / 1.230 / 1.520, A/F 1.062, bores 0.391 = OMi row 851)); OMi = Brennan data (Brennan catalog TFA p51 (MJ-FP-MJ TEE) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2606-04-04-04 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): TAPDRILL@BORE: end-library tap drill of the -04 pipe port = 0.43 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>2026-10-02 (JIC-TEES): stays MISSING ONLY for the female port (TAPDRILL@BORE, PORTDEPTH@BORE): OMi / the catalog print no tap drill and no Brennan STEP of this part is in the repo - every other cell is now filled from OMi (Q-TRANSFER-TAPDRILL; candidates in proposals/) | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2606-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): the female port now takes the end-library tap drill and MS51503 P1 - ASSUMED (one source)</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>2606-04-04-04-FG</t>
         </is>
@@ -1062,32 +1097,62 @@
           <t>2606-06-06-06-FG</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="B11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>2606-06-06-06-FG</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2606-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2606-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / L 1 / Hex Flat / Side 1 ID / Side 3 ID = JIC run leg / female pipe run leg / JIC branch leg / body hex / JIC bores (Brennan TFA catalog p51 drawing M / L / N / Y / B1 / B3; Brennan 2606-08-08-08-FG STEP: 1.520 / 1.230 / 1.520, A/F 1.062, bores 0.391 = OMi row 851)); OMi = Brennan data (Brennan catalog TFA p51 (MJ-FP-MJ TEE) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2606-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): TAPDRILL@BORE: end-library tap drill of the -06 pipe port = 0.57 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>2026-10-02 (JIC-TEES): stays MISSING ONLY for the female port (TAPDRILL@BORE, PORTDEPTH@BORE): OMi / the catalog print no tap drill and no Brennan STEP of this part is in the repo - every other cell is now filled from OMi (Q-TRANSFER-TAPDRILL; candidates in proposals/) | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2606-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): the female port now takes the end-library tap drill and MS51503 P1 - ASSUMED (one source)</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>2606-06-06-06-FG</t>
         </is>
@@ -1099,32 +1164,62 @@
           <t>2606-08-08-08-FG</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="B12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>2606-08-08-08-FG</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2606-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2606-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2606-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): M1_1@DRIVE: OMi Items row 851 M 1 Size = 1.520; N1@DRIVE: OMi Items row 851 M 2 Size = 1.230; M1_3@DRIVE: OMi Items row 851 L 1 Size = 1.520; Y1@HEX: OMi Items row 851 Hex Flat = 1.062; D1@BORE: OMi Items row 851 Side 1 ID = 0.391; D3@BORE: OMi Items row 851 Side 3 ID = 0.391; THDMAJ_B1@DRIVE: 3/4-16 -&gt; 0.75 (end library); THDMAJ_A@DRIVE: 1/2-14 -&gt; 0.84 (end library); THDMAJ_B3@DRIVE: 3/4-16 -&gt; 0.75 (end library); TAPDRILL@BORE: end-library tap drill of the -08 pipe port = 0.7 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2606-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): body from OMi Items row 851, ports from the end library (not from its own Brennan file) - ASSUMED (one source)</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>2606-08-08-08-FG</t>
         </is>
@@ -1136,32 +1231,62 @@
           <t>2606-12-12-12-FG</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="B13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>2606-12-12-12-FG</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / L 1 / Hex Flat / Side 1 ID / Side 3 ID = JIC run leg / female pipe run leg / JIC branch leg / body hex / JIC bores (Brennan TFA catalog p51 drawing M / L / N / Y / B1 / B3; Brennan 2606-08-08-08-FG STEP: 1.520 / 1.230 / 1.520, A/F 1.062, bores 0.391 = OMi row 851)); OMi = Brennan data (Brennan catalog TFA p51 (MJ-FP-MJ TEE) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING; 2026-10-09 (staged): TAPDRILL@BORE: end-library tap drill of the -12 pipe port = 0.91 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>2026-10-02 (JIC-TEES): stays MISSING ONLY for the female port (TAPDRILL@BORE, PORTDEPTH@BORE): OMi / the catalog print no tap drill and no Brennan STEP of this part is in the repo - every other cell is now filled from OMi (Q-TRANSFER-TAPDRILL; candidates in proposals/) | previous: BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | RESOLVED 2026-10-09 (staged): the female port now takes the end-library tap drill and MS51503 P1 - ASSUMED (one source)</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>2606-12-12-12-FG</t>
         </is>
@@ -1173,32 +1298,62 @@
           <t>2606-16-16-16-FG</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="B14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>2606-16-16-16-FG</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2606-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2606-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / L 1 / Hex Flat / Side 1 ID / Side 3 ID = JIC run leg / female pipe run leg / JIC branch leg / body hex / JIC bores (Brennan TFA catalog p51 drawing M / L / N / Y / B1 / B3; Brennan 2606-08-08-08-FG STEP: 1.520 / 1.230 / 1.520, A/F 1.062, bores 0.391 = OMi row 851)); OMi = Brennan data (Brennan catalog TFA p51 (MJ-FP-MJ TEE) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2606-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): TAPDRILL@BORE: end-library tap drill of the -16 pipe port = 1.14 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>2026-10-02 (JIC-TEES): stays MISSING ONLY for the female port (TAPDRILL@BORE, PORTDEPTH@BORE): OMi / the catalog print no tap drill and no Brennan STEP of this part is in the repo - every other cell is now filled from OMi (Q-TRANSFER-TAPDRILL; candidates in proposals/) | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2606-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): the female port now takes the end-library tap drill and MS51503 P1 - ASSUMED (one source)</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>2606-16-16-16-FG</t>
         </is>
